--- a/dados/xlsx/base_de_dados.xlsx
+++ b/dados/xlsx/base_de_dados.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6687DDE5-B1F0-4D25-B31D-5244E2A1D280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C8BDDA-927A-40D7-BAAB-1FDE6BB83931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F38C5BB0-6CAB-4BA1-8646-3EA51DC69E2B}"/>
+    <workbookView xWindow="28680" yWindow="1035" windowWidth="29040" windowHeight="15840" xr2:uid="{F38C5BB0-6CAB-4BA1-8646-3EA51DC69E2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$278</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="438">
   <si>
     <t>CÓD DO PRODUTO</t>
   </si>
@@ -1255,9 +1258,6 @@
     <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ S/ IMÃ S/ CONTROLE S/ CREMALHE</t>
   </si>
   <si>
-    <t>12 UF</t>
-  </si>
-  <si>
     <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ LOG</t>
   </si>
   <si>
@@ -1382,6 +1382,9 @@
   </si>
   <si>
     <t>B. ALUM C/ENCODER</t>
+  </si>
+  <si>
+    <t>15UF</t>
   </si>
 </sst>
 </file>
@@ -1955,16 +1958,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7641DCFD-0FAD-4622-A349-1A7C7861AA22}">
-  <dimension ref="A1:K277"/>
+  <dimension ref="A1:K278"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="116" style="4" customWidth="1"/>
     <col min="3" max="3" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" style="4" bestFit="1" customWidth="1"/>
@@ -2017,7 +2020,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>13</v>
@@ -2049,7 +2052,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>13</v>
@@ -2081,7 +2084,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>20</v>
@@ -2104,7 +2107,7 @@
         <v>2001277</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>11</v>
@@ -2113,7 +2116,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>20</v>
@@ -2145,7 +2148,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>23</v>
@@ -2181,7 +2184,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>23</v>
@@ -2213,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2245,7 +2248,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>26</v>
@@ -2277,7 +2280,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>29</v>
@@ -2309,7 +2312,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>29</v>
@@ -2341,7 +2344,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>32</v>
@@ -2373,7 +2376,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>32</v>
@@ -2402,10 +2405,10 @@
         <v>35</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>38</v>
@@ -2434,10 +2437,10 @@
         <v>35</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>38</v>
@@ -2466,10 +2469,10 @@
         <v>35</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>38</v>
@@ -2501,7 +2504,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>38</v>
@@ -2530,10 +2533,10 @@
         <v>35</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
@@ -2562,10 +2565,10 @@
         <v>47</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
@@ -2597,7 +2600,7 @@
         <v>92</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -2626,10 +2629,10 @@
         <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>38</v>
@@ -2658,10 +2661,10 @@
         <v>47</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -2690,16 +2693,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>40</v>
@@ -2722,16 +2725,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>40</v>
@@ -2754,16 +2757,16 @@
         <v>35</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>40</v>
@@ -2786,16 +2789,16 @@
         <v>35</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>40</v>
@@ -2827,7 +2830,7 @@
         <v>53</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>60</v>
@@ -2859,7 +2862,7 @@
         <v>53</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>40</v>
@@ -2885,13 +2888,13 @@
         <v>92</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>40</v>
@@ -2914,16 +2917,16 @@
         <v>35</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>40</v>
@@ -2949,13 +2952,13 @@
         <v>92</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>40</v>
@@ -2978,10 +2981,10 @@
         <v>47</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>53</v>
@@ -3013,7 +3016,7 @@
         <v>92</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>53</v>
@@ -3042,10 +3045,10 @@
         <v>47</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>53</v>
@@ -3074,10 +3077,10 @@
         <v>47</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>53</v>
@@ -3458,10 +3461,10 @@
         <v>35</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>87</v>
@@ -3490,10 +3493,10 @@
         <v>35</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>87</v>
@@ -3522,10 +3525,10 @@
         <v>35</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>87</v>
@@ -3554,10 +3557,10 @@
         <v>35</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>87</v>
@@ -3589,7 +3592,7 @@
         <v>92</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>87</v>
@@ -3618,10 +3621,10 @@
         <v>35</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>87</v>
@@ -3650,10 +3653,10 @@
         <v>35</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>87</v>
@@ -3682,10 +3685,10 @@
         <v>35</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>87</v>
@@ -3717,7 +3720,7 @@
         <v>92</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>87</v>
@@ -3746,16 +3749,16 @@
         <v>35</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>40</v>
@@ -3781,13 +3784,13 @@
         <v>92</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>40</v>
@@ -3810,16 +3813,16 @@
         <v>35</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>40</v>
@@ -3842,16 +3845,16 @@
         <v>35</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>40</v>
@@ -3874,16 +3877,16 @@
         <v>35</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>40</v>
@@ -3906,16 +3909,16 @@
         <v>35</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>40</v>
@@ -4491,7 +4494,7 @@
         <v>127</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>40</v>
@@ -4523,7 +4526,7 @@
         <v>127</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>40</v>
@@ -4555,7 +4558,7 @@
         <v>127</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>40</v>
@@ -4587,7 +4590,7 @@
         <v>127</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>40</v>
@@ -4619,7 +4622,7 @@
         <v>127</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>40</v>
@@ -4651,7 +4654,7 @@
         <v>127</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>40</v>
@@ -4907,7 +4910,7 @@
         <v>142</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>15</v>
@@ -4939,7 +4942,7 @@
         <v>142</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>15</v>
@@ -4971,7 +4974,7 @@
         <v>142</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>15</v>
@@ -5003,7 +5006,7 @@
         <v>142</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>15</v>
@@ -5035,7 +5038,7 @@
         <v>142</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>15</v>
@@ -5067,7 +5070,7 @@
         <v>142</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>15</v>
@@ -5093,7 +5096,7 @@
         <v>36</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>38</v>
@@ -5125,7 +5128,7 @@
         <v>92</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>151</v>
@@ -5163,7 +5166,7 @@
         <v>153</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>15</v>
@@ -5253,7 +5256,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>20</v>
@@ -5285,7 +5288,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -5317,7 +5320,7 @@
         <v>12</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>32</v>
@@ -5349,7 +5352,7 @@
         <v>92</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>38</v>
@@ -5381,13 +5384,13 @@
         <v>92</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>163</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>40</v>
@@ -5413,7 +5416,7 @@
         <v>12</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>29</v>
@@ -5445,13 +5448,13 @@
         <v>36</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>151</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>40</v>
@@ -5509,13 +5512,13 @@
         <v>36</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>163</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>40</v>
@@ -5547,7 +5550,7 @@
         <v>169</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>40</v>
@@ -5573,7 +5576,7 @@
         <v>92</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>151</v>
@@ -5605,13 +5608,13 @@
         <v>92</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>163</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>74</v>
@@ -5675,7 +5678,7 @@
         <v>155</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>74</v>
@@ -5730,10 +5733,10 @@
         <v>176</v>
       </c>
       <c r="D118" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>38</v>
@@ -5762,16 +5765,16 @@
         <v>176</v>
       </c>
       <c r="D119" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H119" s="7" t="s">
         <v>177</v>
@@ -5858,10 +5861,10 @@
         <v>176</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>87</v>
@@ -5890,16 +5893,16 @@
         <v>176</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H123" s="7" t="s">
         <v>177</v>
@@ -6027,7 +6030,7 @@
         <v>127</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H127" s="7" t="s">
         <v>177</v>
@@ -6091,7 +6094,7 @@
         <v>142</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H129" s="7" t="s">
         <v>189</v>
@@ -6117,7 +6120,7 @@
         <v>12</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>38</v>
@@ -6149,13 +6152,13 @@
         <v>12</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H131" s="7" t="s">
         <v>177</v>
@@ -6245,7 +6248,7 @@
         <v>12</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>87</v>
@@ -6277,13 +6280,13 @@
         <v>12</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H135" s="7" t="s">
         <v>177</v>
@@ -6411,7 +6414,7 @@
         <v>127</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H139" s="7" t="s">
         <v>177</v>
@@ -6475,7 +6478,7 @@
         <v>142</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H141" s="7" t="s">
         <v>189</v>
@@ -6530,16 +6533,16 @@
         <v>176</v>
       </c>
       <c r="D143" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E143" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H143" s="7" t="s">
         <v>177</v>
@@ -6562,16 +6565,16 @@
         <v>176</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H144" s="7" t="s">
         <v>177</v>
@@ -6597,13 +6600,13 @@
         <v>12</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H145" s="7" t="s">
         <v>177</v>
@@ -6629,13 +6632,13 @@
         <v>12</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H146" s="7" t="s">
         <v>177</v>
@@ -6658,10 +6661,10 @@
         <v>176</v>
       </c>
       <c r="D147" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E147" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>38</v>
@@ -6690,10 +6693,10 @@
         <v>176</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>87</v>
@@ -6923,7 +6926,7 @@
         <v>142</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H155" s="7" t="s">
         <v>189</v>
@@ -6978,10 +6981,10 @@
         <v>176</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>87</v>
@@ -7010,16 +7013,16 @@
         <v>176</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>177</v>
@@ -7083,7 +7086,7 @@
         <v>127</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H160" s="7" t="s">
         <v>177</v>
@@ -7109,13 +7112,13 @@
         <v>12</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>229</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H161" s="7" t="s">
         <v>177</v>
@@ -7173,7 +7176,7 @@
         <v>234</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>235</v>
@@ -7205,7 +7208,7 @@
         <v>234</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>238</v>
@@ -7237,7 +7240,7 @@
         <v>234</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>238</v>
@@ -7269,7 +7272,7 @@
         <v>234</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>238</v>
@@ -7333,7 +7336,7 @@
         <v>70</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>87</v>
@@ -7365,7 +7368,7 @@
         <v>12</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>87</v>
@@ -7429,7 +7432,7 @@
         <v>12</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>235</v>
@@ -7557,7 +7560,7 @@
         <v>70</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>38</v>
@@ -7589,13 +7592,13 @@
         <v>12</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>253</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H176" s="7" t="s">
         <v>177</v>
@@ -7621,13 +7624,13 @@
         <v>12</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>253</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H177" s="7" t="s">
         <v>177</v>
@@ -7653,7 +7656,7 @@
         <v>70</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>256</v>
@@ -7685,7 +7688,7 @@
         <v>70</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>258</v>
@@ -7717,7 +7720,7 @@
         <v>12</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>260</v>
@@ -7755,7 +7758,7 @@
         <v>262</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H181" s="5" t="s">
         <v>15</v>
@@ -7781,7 +7784,7 @@
         <v>12</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -7813,7 +7816,7 @@
         <v>12</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>32</v>
@@ -7845,7 +7848,7 @@
         <v>234</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>266</v>
@@ -7877,7 +7880,7 @@
         <v>234</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>268</v>
@@ -8005,7 +8008,7 @@
         <v>36</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>38</v>
@@ -8037,13 +8040,13 @@
         <v>70</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>229</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H190" s="7" t="s">
         <v>177</v>
@@ -8069,13 +8072,13 @@
         <v>70</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>253</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H191" s="7" t="s">
         <v>177</v>
@@ -8107,7 +8110,7 @@
         <v>278</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H192" s="5" t="s">
         <v>189</v>
@@ -8139,7 +8142,7 @@
         <v>169</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>177</v>
@@ -8165,13 +8168,13 @@
         <v>92</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H194" s="5" t="s">
         <v>40</v>
@@ -8197,7 +8200,7 @@
         <v>234</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>266</v>
@@ -8229,7 +8232,7 @@
         <v>70</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>258</v>
@@ -8293,7 +8296,7 @@
         <v>12</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>32</v>
@@ -8331,7 +8334,7 @@
         <v>153</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H199" s="5" t="s">
         <v>15</v>
@@ -8389,7 +8392,7 @@
         <v>70</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F201" s="6" t="s">
         <v>256</v>
@@ -8427,7 +8430,7 @@
         <v>142</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H202" s="7" t="s">
         <v>289</v>
@@ -8549,7 +8552,7 @@
         <v>36</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>87</v>
@@ -8709,10 +8712,10 @@
         <v>92</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G211" s="5" t="s">
         <v>54</v>
@@ -8773,13 +8776,13 @@
         <v>36</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>40</v>
@@ -8802,7 +8805,7 @@
         <v>47</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>37</v>
@@ -8837,7 +8840,7 @@
         <v>12</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>235</v>
@@ -8933,7 +8936,7 @@
         <v>12</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>238</v>
@@ -8965,7 +8968,7 @@
         <v>12</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>305</v>
@@ -9029,7 +9032,7 @@
         <v>12</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>317</v>
@@ -9061,7 +9064,7 @@
         <v>12</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>319</v>
@@ -9093,7 +9096,7 @@
         <v>12</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>317</v>
@@ -9189,7 +9192,7 @@
         <v>12</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>235</v>
@@ -9207,7 +9210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>2001317</v>
       </c>
@@ -9253,7 +9256,7 @@
         <v>12</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>238</v>
@@ -9346,10 +9349,10 @@
         <v>35</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>317</v>
@@ -9413,7 +9416,7 @@
         <v>70</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>335</v>
@@ -9605,7 +9608,7 @@
         <v>12</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>348</v>
@@ -9765,7 +9768,7 @@
         <v>12</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>235</v>
@@ -9829,7 +9832,7 @@
         <v>12</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>366</v>
@@ -9868,7 +9871,7 @@
         <v>12</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>371</v>
@@ -9929,10 +9932,10 @@
         <v>47</v>
       </c>
       <c r="D250" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="E250" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E250" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>375</v>
@@ -9961,10 +9964,10 @@
         <v>47</v>
       </c>
       <c r="D251" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E251" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E251" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>377</v>
@@ -9993,10 +9996,10 @@
         <v>47</v>
       </c>
       <c r="D252" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E252" s="7" t="s">
         <v>430</v>
-      </c>
-      <c r="E252" s="7" t="s">
-        <v>431</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>380</v>
@@ -10022,13 +10025,13 @@
         <v>381</v>
       </c>
       <c r="C253" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E253" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="E253" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>377</v>
@@ -10060,7 +10063,7 @@
         <v>12</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>385</v>
@@ -10098,7 +10101,7 @@
         <v>388</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>54</v>
+        <v>437</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>40</v>
@@ -10156,7 +10159,7 @@
         <v>12</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>393</v>
@@ -10185,16 +10188,16 @@
         <v>176</v>
       </c>
       <c r="D258" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E258" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E258" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>380</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>177</v>
@@ -10211,22 +10214,22 @@
         <v>2006148</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D259" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E259" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E259" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>380</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>177</v>
@@ -10243,7 +10246,7 @@
         <v>2006137</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>176</v>
@@ -10255,13 +10258,13 @@
         <v>206</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G260" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I260" s="5" t="s">
         <v>149</v>
@@ -10275,19 +10278,19 @@
         <v>2006153</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>349</v>
@@ -10302,12 +10305,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>2006155</v>
       </c>
       <c r="B262" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C262" s="5" t="s">
         <v>351</v>
@@ -10339,10 +10342,10 @@
         <v>2001309</v>
       </c>
       <c r="B263" t="s">
+        <v>402</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>403</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>70</v>
@@ -10366,12 +10369,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>2001348</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C264" s="5" t="s">
         <v>370</v>
@@ -10380,10 +10383,10 @@
         <v>384</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>236</v>
@@ -10403,7 +10406,7 @@
         <v>2009011</v>
       </c>
       <c r="B265" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>351</v>
@@ -10412,13 +10415,13 @@
         <v>70</v>
       </c>
       <c r="E265" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F265" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="F265" s="5" t="s">
+      <c r="G265" s="5" t="s">
         <v>409</v>
-      </c>
-      <c r="G265" s="5" t="s">
-        <v>410</v>
       </c>
       <c r="H265" s="5" t="s">
         <v>354</v>
@@ -10435,22 +10438,22 @@
         <v>2009006</v>
       </c>
       <c r="B266" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D266" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F266" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="G266" s="5" t="s">
         <v>412</v>
-      </c>
-      <c r="G266" s="5" t="s">
-        <v>413</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>354</v>
@@ -10467,22 +10470,22 @@
         <v>2009007</v>
       </c>
       <c r="B267" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D267" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E267" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F267" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="F267" s="5" t="s">
-        <v>409</v>
-      </c>
       <c r="G267" s="5" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="H267" s="5" t="s">
         <v>354</v>
@@ -10499,7 +10502,7 @@
         <v>2005039</v>
       </c>
       <c r="B268" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -10507,7 +10510,7 @@
         <v>2005041</v>
       </c>
       <c r="B269" s="21" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -10515,7 +10518,7 @@
         <v>2005040</v>
       </c>
       <c r="B270" s="21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -10523,7 +10526,7 @@
         <v>2005036</v>
       </c>
       <c r="B271" s="21" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -10531,7 +10534,7 @@
         <v>2005049</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -10539,7 +10542,7 @@
         <v>2005038</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -10547,7 +10550,7 @@
         <v>2005037</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -10555,7 +10558,7 @@
         <v>2006156</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C275" s="5" t="s">
         <v>351</v>
@@ -10587,7 +10590,7 @@
         <v>2001347</v>
       </c>
       <c r="B276" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C276" s="5" t="s">
         <v>383</v>
@@ -10596,13 +10599,13 @@
         <v>384</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>386</v>
@@ -10619,19 +10622,19 @@
         <v>2006151</v>
       </c>
       <c r="B277" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D277" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="F277" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="E277" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>349</v>
@@ -10646,7 +10649,40 @@
         <v>17</v>
       </c>
     </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="3">
+        <v>2006152</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H278" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="J278" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:K278" xr:uid="{7641DCFD-0FAD-4622-A349-1A7C7861AA22}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>